--- a/output/pdf_financials_xlsx/WELL.xlsx
+++ b/output/pdf_financials_xlsx/WELL.xlsx
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.00169</v>
+        <v>-0.00169</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.054313</v>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.00169</v>
+        <v>-0.00169</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.054313</v>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.00169</v>
+        <v>-0.00169</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.054313</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.00169</v>
+        <v>-0.00169</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.054313</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.00169</v>
+        <v>-0.00169</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.054313</v>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5046,22 +5046,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0348</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.059994</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.059994</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.059994</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.07284400000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.127344</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>1.292928</v>
@@ -5079,10 +5079,10 @@
         <v>51.765</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>54.048</v>
+        <v>21.578</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>27.468</v>
       </c>
     </row>
     <row r="93">
@@ -10186,7 +10186,11 @@
           <t>Share-based payments reserve 21</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -22866,7 +22870,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -26532,7 +26540,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -28754,7 +28766,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -54849,7 +54865,7 @@
         <v>-20.812</v>
       </c>
       <c r="R558" s="5" t="n">
-        <v>35.509</v>
+        <v>-35.509</v>
       </c>
     </row>
     <row r="559">
@@ -71560,10 +71576,10 @@
         </is>
       </c>
       <c r="E757" s="5" t="n">
-        <v>0.00169</v>
+        <v>-0.00169</v>
       </c>
       <c r="F757" s="5" t="n">
-        <v>0.054313</v>
+        <v>-0.054313</v>
       </c>
       <c r="G757" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WELL.xlsx
+++ b/output/pdf_financials_xlsx/WELL.xlsx
@@ -943,46 +943,46 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001489</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00167</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004763</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00506</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002693</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000674</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.057843</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.241402</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.649</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.763</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>1.272</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>1.715</v>
       </c>
     </row>
     <row r="13">
@@ -1774,46 +1774,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.00169</v>
+        <v>-0.003179</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.054313</v>
+        <v>-0.055983</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.11859</v>
+        <v>-0.123353</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.035862</v>
+        <v>-0.040922</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.145929</v>
+        <v>-0.148622</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.585396</v>
+        <v>-0.58607</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5.566359</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.809887</v>
+        <v>-2.86773</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-7.829149</v>
+        <v>-8.070551</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-25.485</v>
+        <v>-26.04</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>17.525</v>
+        <v>16.876</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>19.497</v>
+        <v>18.734</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>8.992000000000001</v>
+        <v>7.72</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>5.308</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="28">
@@ -1872,46 +1872,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.00169</v>
+        <v>-0.003179</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.054313</v>
+        <v>-0.055983</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.11859</v>
+        <v>-0.123353</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.035862</v>
+        <v>-0.040922</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.145929</v>
+        <v>-0.148622</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.585396</v>
+        <v>-0.58607</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.566359</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.831874</v>
+        <v>-2.889717</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-9.984195</v>
+        <v>-10.225597</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-64.19499999999999</v>
+        <v>-64.75</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-37.678</v>
+        <v>-38.327</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-41.271</v>
+        <v>-42.034</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-63.314</v>
+        <v>-64.586</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-88.45399999999999</v>
+        <v>-90.169</v>
       </c>
     </row>
     <row r="30">
@@ -1946,31 +1946,31 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-205.6756177513254</v>
+        <v>-205.9124238900151</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-1341.756898779335</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-26.81749654349514</v>
+        <v>-27.36526259967045</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-30.42961609388036</v>
+        <v>-31.16535594915111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-21.23384183855731</v>
+        <v>-21.41741972188778</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-6.620210283658036</v>
+        <v>-6.734242782041551</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-5.318057764021575</v>
+        <v>-5.416375664580042</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-6.884291194405059</v>
+        <v>-7.022598968345786</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-6.317335140721293</v>
+        <v>-6.4398194802236</v>
       </c>
     </row>
     <row r="31">
@@ -2095,25 +2095,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.170835</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.139672</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.5562550000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.525003</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.327994</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.036958</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.266474</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.334208</v>
@@ -2131,10 +2131,10 @@
         <v>48.908</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>43.423</v>
+        <v>131.669</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>133.755</v>
       </c>
     </row>
     <row r="35">
@@ -2193,25 +2193,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.170835</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.139672</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.5562550000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.525003</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.327994</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.036958</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.266474</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.334208</v>
@@ -2229,10 +2229,10 @@
         <v>48.908</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>43.423</v>
+        <v>131.669</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>133.755</v>
       </c>
     </row>
     <row r="37">
@@ -2781,25 +2781,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.185835</v>
+        <v>0.015</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.195837</v>
+        <v>0.056165</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.5562550000000001</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.525003</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.361224</v>
+        <v>0.03323</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.07642500000000001</v>
+        <v>0.039467</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.303343</v>
+        <v>0.036869</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.125613</v>
@@ -2817,10 +2817,10 @@
         <v>21.685</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>115.494</v>
+        <v>27.248</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>196.196</v>
+        <v>62.441</v>
       </c>
     </row>
     <row r="49">
@@ -6665,22 +6665,22 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-2.082526</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-5.657</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-10.276</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-13.41</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-18.781</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-25.655</v>
       </c>
     </row>
     <row r="125">
@@ -6716,22 +6716,22 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-2.082526</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-5.657</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-10.276</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-13.41</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-18.781</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-25.655</v>
       </c>
     </row>
     <row r="126">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E222" s="5" t="n">
@@ -32486,7 +32486,11 @@
           <t>Lease payments 19</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -35610,7 +35614,11 @@
           <t>Lease payments (Note 19(a))</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -37640,7 +37648,11 @@
           <t>Lease payments (Note 18(a))</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -42858,7 +42870,11 @@
           <t>Lease payments (Note 14)</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -52588,7 +52604,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -52676,7 +52692,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -56238,7 +56254,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -56318,7 +56334,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -69286,7 +69302,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -70636,7 +70652,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E746" s="5" t="n">

--- a/output/pdf_financials_xlsx/WELL.xlsx
+++ b/output/pdf_financials_xlsx/WELL.xlsx
@@ -1215,7 +1215,7 @@
         <v>0.035235</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-5.802</v>
+        <v>5.802</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-1.15</v>
@@ -1412,7 +1412,7 @@
         <v>-5.566359</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-2.809887</v>
+        <v>-2.595448</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-7.793914</v>
@@ -1424,10 +1424,10 @@
         <v>18.675</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>16.637</v>
+        <v>-32.141</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>29.096</v>
+        <v>-27.426</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>4.462</v>
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-0.214439</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>-0.596</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>-0.054</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>0</v>
@@ -2263,10 +2263,10 @@
         <v>0.048737</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>1.037487</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>1918.887</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
@@ -2422,13 +2422,13 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>7.581</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>5.722</v>
       </c>
     </row>
     <row r="41">
@@ -3225,19 +3225,19 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>24537.267</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>99.738</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>98.249</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>144.582</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>168.708</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>0</v>
@@ -3274,19 +3274,19 @@
         <v>0</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>3645.681</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>11.187</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>15.714</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>42.042</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>66.946</v>
       </c>
       <c r="O57" s="3" t="n">
         <v>0</v>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002909</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.002909</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
@@ -5479,10 +5479,10 @@
         <v>-0.03627</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>2.167876</v>
+        <v>2.228277</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>4.060804</v>
+        <v>4.157013</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0</v>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.032424</v>
+        <v>0.029515</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.00636</v>
+        <v>0.009268999999999999</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.00461</v>
@@ -5734,10 +5734,10 @@
         <v>-0.105041</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>2.167876</v>
+        <v>2.228277</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>4.060804</v>
+        <v>4.157013</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>-11.298</v>
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>0</v>
+        <v>11.606</v>
       </c>
     </row>
     <row r="109">
@@ -6202,10 +6202,10 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>16.51</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>11.563</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -29790,7 +29790,11 @@
           <t>Impairment charge 14 15</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -37054,7 +37058,11 @@
           <t>Proceeds from disposal of investments (Note 23)</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -42108,7 +42116,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -45338,7 +45350,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -47902,7 +47918,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -49458,7 +49478,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -56668,7 +56692,11 @@
           <t>Income tax recovery (expense) (Note 20)</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
@@ -59570,7 +59598,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr">
         <is>
           <t>-</t>
@@ -59654,7 +59686,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D616" t="inlineStr"/>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E616" t="inlineStr">
         <is>
           <t>-</t>
@@ -59711,7 +59747,7 @@
         </is>
       </c>
       <c r="P616" s="5" t="n">
-        <v>0.596</v>
+        <v>-0.596</v>
       </c>
       <c r="Q616" s="5" t="n">
         <v>-0.054</v>
@@ -61942,7 +61978,11 @@
           <t>Income tax recovery (expense) (Note 19)</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
@@ -66158,7 +66198,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D693" t="inlineStr"/>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E693" t="inlineStr">
         <is>
           <t>-</t>
@@ -66242,7 +66286,11 @@
           <t>Net loss from discontinued operations (Note 25)</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr">
         <is>
           <t>-</t>
